--- a/docs/effort-estimation.xlsx
+++ b/docs/effort-estimation.xlsx
@@ -8,12 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vikto\Documents\HTL\3IHIF\WMC\room-food\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{78253719-4C00-4EBA-A98C-09C6E7FC5430}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A21A5851-18F3-4B60-AD71-BF29C11500FD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{5CD19CBD-F40D-4B07-8DFB-09D007D4B786}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{5CD19CBD-F40D-4B07-8DFB-09D007D4B786}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sprint 1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sprint 2" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -36,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="102" uniqueCount="46">
   <si>
     <t>Task</t>
   </si>
@@ -123,6 +124,57 @@
   </si>
   <si>
     <t>Design</t>
+  </si>
+  <si>
+    <t>Login hashing and salting</t>
+  </si>
+  <si>
+    <t>Cookies for account</t>
+  </si>
+  <si>
+    <t>Add possibility to delete your account</t>
+  </si>
+  <si>
+    <t>Add a log out button</t>
+  </si>
+  <si>
+    <t>Adding new properties to user</t>
+  </si>
+  <si>
+    <t>Adding profile page</t>
+  </si>
+  <si>
+    <t>Add functionality for editing an existing meal</t>
+  </si>
+  <si>
+    <t>Calendar design for room view</t>
+  </si>
+  <si>
+    <t>Room backend</t>
+  </si>
+  <si>
+    <t>Create room frontend</t>
+  </si>
+  <si>
+    <t>Edit room frontend</t>
+  </si>
+  <si>
+    <t>Delete room frontend</t>
+  </si>
+  <si>
+    <t>Room overview</t>
+  </si>
+  <si>
+    <t>Invite functionality</t>
+  </si>
+  <si>
+    <t>Control access to pages if not logged in</t>
+  </si>
+  <si>
+    <t>Add error page</t>
+  </si>
+  <si>
+    <t>Unit tests</t>
   </si>
 </sst>
 </file>
@@ -188,7 +240,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -212,12 +264,58 @@
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Accent1" xfId="1" builtinId="29"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="14">
+  <dxfs count="28">
+    <dxf>
+      <numFmt numFmtId="1" formatCode="0"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
     <dxf>
       <numFmt numFmtId="1" formatCode="0"/>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
@@ -275,36 +373,73 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{3FF54A41-9CC2-4AA2-8F76-5A18AE412277}" name="Table1" displayName="Table1" ref="A1:F15" totalsRowShown="0" headerRowDxfId="13">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{3FF54A41-9CC2-4AA2-8F76-5A18AE412277}" name="Table1" displayName="Table1" ref="A1:F15" totalsRowShown="0" headerRowDxfId="27">
   <tableColumns count="6">
-    <tableColumn id="1" xr3:uid="{BD104E6C-3FB2-4028-B39E-1642A4E103F5}" name="Task" dataDxfId="12"/>
-    <tableColumn id="2" xr3:uid="{660AA389-84BF-4073-B3DF-146936FB4E81}" name="Orig. Est." dataDxfId="11"/>
-    <tableColumn id="3" xr3:uid="{D378DE41-A349-4E73-9DC6-E2AD96D7D4A4}" name="Cur. Est." dataDxfId="10"/>
-    <tableColumn id="4" xr3:uid="{946D4402-72BC-47FB-BC27-9032EAD1C753}" name="Effort" dataDxfId="9"/>
-    <tableColumn id="5" xr3:uid="{AC96E08D-31C6-4AAC-9707-12BB2EE31872}" name="Remain" dataDxfId="8"/>
-    <tableColumn id="6" xr3:uid="{1EC34EF9-51C7-4321-9E8F-6F0F5D21B221}" name="Responsible" dataDxfId="7"/>
+    <tableColumn id="1" xr3:uid="{BD104E6C-3FB2-4028-B39E-1642A4E103F5}" name="Task" dataDxfId="26"/>
+    <tableColumn id="2" xr3:uid="{660AA389-84BF-4073-B3DF-146936FB4E81}" name="Orig. Est." dataDxfId="25"/>
+    <tableColumn id="3" xr3:uid="{D378DE41-A349-4E73-9DC6-E2AD96D7D4A4}" name="Cur. Est." dataDxfId="24"/>
+    <tableColumn id="4" xr3:uid="{946D4402-72BC-47FB-BC27-9032EAD1C753}" name="Effort" dataDxfId="23"/>
+    <tableColumn id="5" xr3:uid="{AC96E08D-31C6-4AAC-9707-12BB2EE31872}" name="Remain" dataDxfId="22"/>
+    <tableColumn id="6" xr3:uid="{1EC34EF9-51C7-4321-9E8F-6F0F5D21B221}" name="Responsible" dataDxfId="21"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{B86BA106-B777-4F33-87EE-B404BD463F96}" name="Table2" displayName="Table2" ref="H1:J3" totalsRowShown="0" dataDxfId="6">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{B86BA106-B777-4F33-87EE-B404BD463F96}" name="Table2" displayName="Table2" ref="H1:J3" totalsRowShown="0" dataDxfId="20">
   <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{FFB5BE72-43DE-47B5-977E-AEBEB8293E0A}" name="Product Owner" dataDxfId="5"/>
-    <tableColumn id="2" xr3:uid="{9114A611-9993-47EF-A53E-7D29A6F4A229}" name="Scrum Master" dataDxfId="4"/>
-    <tableColumn id="3" xr3:uid="{C21A4105-83F6-4202-B883-337A0BCDDCFE}" name="Team Members" dataDxfId="3"/>
+    <tableColumn id="1" xr3:uid="{FFB5BE72-43DE-47B5-977E-AEBEB8293E0A}" name="Product Owner" dataDxfId="19"/>
+    <tableColumn id="2" xr3:uid="{9114A611-9993-47EF-A53E-7D29A6F4A229}" name="Scrum Master" dataDxfId="18"/>
+    <tableColumn id="3" xr3:uid="{C21A4105-83F6-4202-B883-337A0BCDDCFE}" name="Team Members" dataDxfId="17"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight12" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{2AD5516C-E55D-4EA5-B211-AE20A2CFBCC4}" name="Table14" displayName="Table14" ref="A17:B21" totalsRowShown="0" headerRowDxfId="2">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{2AD5516C-E55D-4EA5-B211-AE20A2CFBCC4}" name="Table14" displayName="Table14" ref="A17:B21" totalsRowShown="0" headerRowDxfId="16">
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{826D21A2-3DD6-443C-A7D9-4D7D69D4D081}" name="User" dataDxfId="1"/>
-    <tableColumn id="2" xr3:uid="{952CF9E3-2B94-4AAB-A033-27B3D19CDA85}" name="Total" dataDxfId="0">
+    <tableColumn id="1" xr3:uid="{826D21A2-3DD6-443C-A7D9-4D7D69D4D081}" name="User" dataDxfId="15"/>
+    <tableColumn id="2" xr3:uid="{952CF9E3-2B94-4AAB-A033-27B3D19CDA85}" name="Total" dataDxfId="14">
       <calculatedColumnFormula>SUMIF($F$2:$F$14,Table14[[#This Row],[User]],$C$2:$C$14)</calculatedColumnFormula>
+    </tableColumn>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleLight9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{4572189F-29BF-400F-A010-14B1A3F85040}" name="Table15" displayName="Table15" ref="A1:F19" totalsRowShown="0" headerRowDxfId="13">
+  <tableColumns count="6">
+    <tableColumn id="1" xr3:uid="{F23DD78E-9832-4D69-9866-88B23B4C7197}" name="Task" dataDxfId="12"/>
+    <tableColumn id="2" xr3:uid="{12CE1293-031B-41E3-A384-99D9E64BE2AC}" name="Orig. Est." dataDxfId="11"/>
+    <tableColumn id="3" xr3:uid="{361FACD2-604B-42E1-951F-E479A19E4F68}" name="Cur. Est." dataDxfId="10"/>
+    <tableColumn id="4" xr3:uid="{04FF6573-A625-4DDA-A8A5-A0102C89B784}" name="Effort" dataDxfId="9"/>
+    <tableColumn id="5" xr3:uid="{4D2C2CFC-85E4-43DF-AE5D-FBB5274E2BB6}" name="Remain" dataDxfId="8"/>
+    <tableColumn id="6" xr3:uid="{65747612-EF52-4B83-9BB7-7096DDBA66E6}" name="Responsible" dataDxfId="7"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleLight9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{5198A3BB-CD99-4A50-BAE4-D470DD639E89}" name="Table26" displayName="Table26" ref="H1:J3" totalsRowShown="0" dataDxfId="6">
+  <tableColumns count="3">
+    <tableColumn id="1" xr3:uid="{F4ADF128-D9F1-4DF5-9ABE-6F3FCB334CE2}" name="Product Owner" dataDxfId="5"/>
+    <tableColumn id="2" xr3:uid="{EEED3716-B105-46BE-B2AA-AB2245881A37}" name="Scrum Master" dataDxfId="4"/>
+    <tableColumn id="3" xr3:uid="{E5E1E5D5-8404-49D4-ABF7-6AE9835F2022}" name="Team Members" dataDxfId="3"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleLight12" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{D3470464-FD92-4998-AE54-230A2D4B8316}" name="Table147" displayName="Table147" ref="A21:B25" totalsRowShown="0" headerRowDxfId="2">
+  <tableColumns count="2">
+    <tableColumn id="1" xr3:uid="{1149A006-89B6-4B0D-9155-4EE279EE42E5}" name="User" dataDxfId="1"/>
+    <tableColumn id="2" xr3:uid="{4E4E6EE8-7212-48D4-B6CD-F579FD6C69B8}" name="Total" dataDxfId="0">
+      <calculatedColumnFormula>SUMIF($F$2:$F$18,Table147[[#This Row],[User]],$C$2:$C$18)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
@@ -739,7 +874,8 @@
         <v>6</v>
       </c>
       <c r="E4" s="4">
-        <v>6</v>
+        <f>Table1[[#This Row],[Cur. Est.]]-Table1[[#This Row],[Effort]]</f>
+        <v>0</v>
       </c>
       <c r="F4" s="3" t="s">
         <v>13</v>
@@ -960,20 +1096,20 @@
         <v>19</v>
       </c>
       <c r="B15" s="7">
-        <f>SUM(B2:B9)</f>
+        <f>SUM(B2:B14)</f>
         <v>22</v>
       </c>
       <c r="C15" s="7">
-        <f>SUM(C2:C9)</f>
-        <v>45</v>
+        <f t="shared" ref="C15:E15" si="0">SUM(C2:C14)</f>
+        <v>54.5</v>
       </c>
       <c r="D15" s="7">
-        <f>SUM(D2:D9)</f>
-        <v>45</v>
+        <f t="shared" si="0"/>
+        <v>54.5</v>
       </c>
       <c r="E15" s="7">
-        <f>SUM(E2:E9)</f>
-        <v>6</v>
+        <f t="shared" si="0"/>
+        <v>0</v>
       </c>
       <c r="F15" s="6" t="s">
         <v>20</v>
@@ -1000,7 +1136,7 @@
       <c r="A19" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="B19" s="4">
+      <c r="B19" s="8">
         <f>SUMIF($F$2:$F$14,Table14[[#This Row],[User]],$C$2:$C$14)</f>
         <v>19.5</v>
       </c>
@@ -1032,4 +1168,512 @@
     <tablePart r:id="rId3"/>
   </tableParts>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{015E3E00-EDB7-4DA6-9F4F-93B305E2C6ED}">
+  <dimension ref="A1:J25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="36.109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="3" width="8.88671875" customWidth="1"/>
+    <col min="5" max="5" width="8.88671875" customWidth="1"/>
+    <col min="6" max="6" width="16.21875" customWidth="1"/>
+    <col min="7" max="7" width="7.33203125" customWidth="1"/>
+    <col min="8" max="9" width="15.5546875" customWidth="1"/>
+    <col min="10" max="10" width="15.33203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="H1" t="s">
+        <v>10</v>
+      </c>
+      <c r="I1" t="s">
+        <v>11</v>
+      </c>
+      <c r="J1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>29</v>
+      </c>
+      <c r="B2" s="4">
+        <v>2</v>
+      </c>
+      <c r="C2" s="4">
+        <f>Table15[[#This Row],[Orig. Est.]]</f>
+        <v>2</v>
+      </c>
+      <c r="D2" s="4">
+        <v>0</v>
+      </c>
+      <c r="E2" s="4">
+        <f>Table15[[#This Row],[Cur. Est.]]-Table15[[#This Row],[Effort]]</f>
+        <v>2</v>
+      </c>
+      <c r="F2" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="H2" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="I2" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="J2" s="3" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>30</v>
+      </c>
+      <c r="B3" s="8">
+        <v>2.5</v>
+      </c>
+      <c r="C3" s="4">
+        <f>Table15[[#This Row],[Orig. Est.]]</f>
+        <v>2.5</v>
+      </c>
+      <c r="D3" s="4">
+        <v>0</v>
+      </c>
+      <c r="E3" s="4">
+        <f>Table15[[#This Row],[Cur. Est.]]-Table15[[#This Row],[Effort]]</f>
+        <v>2.5</v>
+      </c>
+      <c r="F3" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="H3" s="3"/>
+      <c r="I3" s="3"/>
+      <c r="J3" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>31</v>
+      </c>
+      <c r="B4" s="4">
+        <v>3</v>
+      </c>
+      <c r="C4" s="4">
+        <f>Table15[[#This Row],[Orig. Est.]]</f>
+        <v>3</v>
+      </c>
+      <c r="D4" s="4">
+        <v>0</v>
+      </c>
+      <c r="E4" s="4">
+        <f>Table15[[#This Row],[Cur. Est.]]-Table15[[#This Row],[Effort]]</f>
+        <v>3</v>
+      </c>
+      <c r="F4" s="9" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>32</v>
+      </c>
+      <c r="B5" s="4">
+        <v>3</v>
+      </c>
+      <c r="C5" s="4">
+        <f>Table15[[#This Row],[Orig. Est.]]</f>
+        <v>3</v>
+      </c>
+      <c r="D5" s="4">
+        <v>0</v>
+      </c>
+      <c r="E5" s="4">
+        <f>Table15[[#This Row],[Cur. Est.]]-Table15[[#This Row],[Effort]]</f>
+        <v>3</v>
+      </c>
+      <c r="F5" s="9" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>33</v>
+      </c>
+      <c r="B6" s="4">
+        <v>4</v>
+      </c>
+      <c r="C6" s="4">
+        <f>Table15[[#This Row],[Orig. Est.]]</f>
+        <v>4</v>
+      </c>
+      <c r="D6" s="4">
+        <v>0</v>
+      </c>
+      <c r="E6" s="4">
+        <f>Table15[[#This Row],[Cur. Est.]]-Table15[[#This Row],[Effort]]</f>
+        <v>4</v>
+      </c>
+      <c r="F6" s="9" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>34</v>
+      </c>
+      <c r="B7" s="4">
+        <v>4</v>
+      </c>
+      <c r="C7" s="4">
+        <f>Table15[[#This Row],[Orig. Est.]]</f>
+        <v>4</v>
+      </c>
+      <c r="D7" s="4">
+        <v>0</v>
+      </c>
+      <c r="E7" s="4">
+        <f>Table15[[#This Row],[Cur. Est.]]-Table15[[#This Row],[Effort]]</f>
+        <v>4</v>
+      </c>
+      <c r="F7" s="9" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>35</v>
+      </c>
+      <c r="B8" s="4">
+        <v>2</v>
+      </c>
+      <c r="C8" s="4">
+        <f>Table15[[#This Row],[Orig. Est.]]</f>
+        <v>2</v>
+      </c>
+      <c r="D8" s="4">
+        <v>0</v>
+      </c>
+      <c r="E8" s="4">
+        <f>Table15[[#This Row],[Cur. Est.]]-Table15[[#This Row],[Effort]]</f>
+        <v>2</v>
+      </c>
+      <c r="F8" s="9" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>36</v>
+      </c>
+      <c r="B9" s="4">
+        <v>4</v>
+      </c>
+      <c r="C9" s="4">
+        <v>6</v>
+      </c>
+      <c r="D9" s="4">
+        <v>0</v>
+      </c>
+      <c r="E9" s="4">
+        <f>Table15[[#This Row],[Cur. Est.]]-Table15[[#This Row],[Effort]]</f>
+        <v>6</v>
+      </c>
+      <c r="F9" s="9" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
+        <v>37</v>
+      </c>
+      <c r="B10" s="4">
+        <v>4</v>
+      </c>
+      <c r="C10" s="4">
+        <f>Table15[[#This Row],[Orig. Est.]]</f>
+        <v>4</v>
+      </c>
+      <c r="D10" s="4">
+        <v>0</v>
+      </c>
+      <c r="E10" s="4">
+        <f>Table15[[#This Row],[Cur. Est.]]-Table15[[#This Row],[Effort]]</f>
+        <v>4</v>
+      </c>
+      <c r="F10" s="9" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
+        <v>38</v>
+      </c>
+      <c r="B11" s="4">
+        <v>3</v>
+      </c>
+      <c r="C11" s="4">
+        <f>Table15[[#This Row],[Orig. Est.]]</f>
+        <v>3</v>
+      </c>
+      <c r="D11" s="4">
+        <v>0</v>
+      </c>
+      <c r="E11" s="4">
+        <f>Table15[[#This Row],[Cur. Est.]]-Table15[[#This Row],[Effort]]</f>
+        <v>3</v>
+      </c>
+      <c r="F11" s="9" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
+        <v>39</v>
+      </c>
+      <c r="B12" s="4">
+        <v>1</v>
+      </c>
+      <c r="C12" s="4">
+        <f>Table15[[#This Row],[Orig. Est.]]</f>
+        <v>1</v>
+      </c>
+      <c r="D12" s="4">
+        <v>0</v>
+      </c>
+      <c r="E12" s="4">
+        <f>Table15[[#This Row],[Cur. Est.]]-Table15[[#This Row],[Effort]]</f>
+        <v>1</v>
+      </c>
+      <c r="F12" s="9" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A13" t="s">
+        <v>40</v>
+      </c>
+      <c r="B13" s="4">
+        <v>1</v>
+      </c>
+      <c r="C13" s="4">
+        <f>Table15[[#This Row],[Orig. Est.]]</f>
+        <v>1</v>
+      </c>
+      <c r="D13" s="4">
+        <v>0</v>
+      </c>
+      <c r="E13" s="4">
+        <f>Table15[[#This Row],[Cur. Est.]]-Table15[[#This Row],[Effort]]</f>
+        <v>1</v>
+      </c>
+      <c r="F13" s="9" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A14" t="s">
+        <v>41</v>
+      </c>
+      <c r="B14" s="4">
+        <v>3</v>
+      </c>
+      <c r="C14" s="4">
+        <f>Table15[[#This Row],[Orig. Est.]]</f>
+        <v>3</v>
+      </c>
+      <c r="D14" s="4">
+        <v>0</v>
+      </c>
+      <c r="E14" s="4">
+        <f>Table15[[#This Row],[Cur. Est.]]-Table15[[#This Row],[Effort]]</f>
+        <v>3</v>
+      </c>
+      <c r="F14" s="9" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A15" t="s">
+        <v>42</v>
+      </c>
+      <c r="B15" s="4">
+        <v>3</v>
+      </c>
+      <c r="C15" s="4">
+        <f>Table15[[#This Row],[Orig. Est.]]</f>
+        <v>3</v>
+      </c>
+      <c r="D15" s="4">
+        <v>0</v>
+      </c>
+      <c r="E15" s="4">
+        <f>Table15[[#This Row],[Cur. Est.]]-Table15[[#This Row],[Effort]]</f>
+        <v>3</v>
+      </c>
+      <c r="F15" s="9" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A16" t="s">
+        <v>43</v>
+      </c>
+      <c r="B16" s="4">
+        <v>2</v>
+      </c>
+      <c r="C16" s="4">
+        <f>Table15[[#This Row],[Orig. Est.]]</f>
+        <v>2</v>
+      </c>
+      <c r="D16" s="4">
+        <v>0</v>
+      </c>
+      <c r="E16" s="4">
+        <f>Table15[[#This Row],[Cur. Est.]]-Table15[[#This Row],[Effort]]</f>
+        <v>2</v>
+      </c>
+      <c r="F16" s="9" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A17" t="s">
+        <v>44</v>
+      </c>
+      <c r="B17" s="4">
+        <v>1</v>
+      </c>
+      <c r="C17" s="4">
+        <f>Table15[[#This Row],[Orig. Est.]]</f>
+        <v>1</v>
+      </c>
+      <c r="D17" s="4">
+        <v>0</v>
+      </c>
+      <c r="E17" s="4">
+        <f>Table15[[#This Row],[Cur. Est.]]-Table15[[#This Row],[Effort]]</f>
+        <v>1</v>
+      </c>
+      <c r="F17" s="9" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A18" t="s">
+        <v>45</v>
+      </c>
+      <c r="B18" s="4">
+        <v>2</v>
+      </c>
+      <c r="C18" s="4">
+        <f>Table15[[#This Row],[Orig. Est.]]</f>
+        <v>2</v>
+      </c>
+      <c r="D18" s="4">
+        <v>0</v>
+      </c>
+      <c r="E18" s="4">
+        <f>Table15[[#This Row],[Cur. Est.]]-Table15[[#This Row],[Effort]]</f>
+        <v>2</v>
+      </c>
+      <c r="F18" s="9" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A19" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="B19" s="7">
+        <f>SUM(B2:B18)</f>
+        <v>44.5</v>
+      </c>
+      <c r="C19" s="7">
+        <f t="shared" ref="C19:E19" si="0">SUM(C2:C18)</f>
+        <v>46.5</v>
+      </c>
+      <c r="D19" s="7">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="E19" s="7">
+        <f t="shared" si="0"/>
+        <v>46.5</v>
+      </c>
+      <c r="F19" s="6" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A21" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A22" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B22" s="4">
+        <f>SUMIF($F$2:$F$18,Table147[[#This Row],[User]],$C$2:$C$18)</f>
+        <v>13</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A23" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B23" s="4">
+        <f>SUMIF($F$2:$F$18,Table147[[#This Row],[User]],$C$2:$C$18)</f>
+        <v>12</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A24" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B24" s="4">
+        <f>SUMIF($F$2:$F$18,Table147[[#This Row],[User]],$C$2:$C$18)</f>
+        <v>11</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A25" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B25" s="4">
+        <f>SUMIF($F$2:$F$18,Table147[[#This Row],[User]],$C$2:$C$18)</f>
+        <v>10.5</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <tableParts count="3">
+    <tablePart r:id="rId1"/>
+    <tablePart r:id="rId2"/>
+    <tablePart r:id="rId3"/>
+  </tableParts>
+</worksheet>
 </file>
--- a/docs/effort-estimation.xlsx
+++ b/docs/effort-estimation.xlsx
@@ -1,20 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vikto\Documents\HTL\3IHIF\WMC\room-food\docs\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vikto\Documents\HTL\3IHIF\WMC\room-food-docs\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A21A5851-18F3-4B60-AD71-BF29C11500FD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{766C7670-7861-4630-9AAD-211BA736D459}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{5CD19CBD-F40D-4B07-8DFB-09D007D4B786}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{5CD19CBD-F40D-4B07-8DFB-09D007D4B786}"/>
   </bookViews>
   <sheets>
     <sheet name="Sprint 1" sheetId="1" r:id="rId1"/>
     <sheet name="Sprint 2" sheetId="2" r:id="rId2"/>
+    <sheet name="Sprint 3" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -37,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="102" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="155" uniqueCount="57">
   <si>
     <t>Task</t>
   </si>
@@ -175,6 +176,39 @@
   </si>
   <si>
     <t>Unit tests</t>
+  </si>
+  <si>
+    <t>Display information when meal clicked</t>
+  </si>
+  <si>
+    <t>Fix account deleting</t>
+  </si>
+  <si>
+    <t>Improve room overview</t>
+  </si>
+  <si>
+    <t>Improve calendar design for room view</t>
+  </si>
+  <si>
+    <t>Manage room members</t>
+  </si>
+  <si>
+    <t>Improve create room frontend</t>
+  </si>
+  <si>
+    <t>Update product backlog</t>
+  </si>
+  <si>
+    <t>Effort plan</t>
+  </si>
+  <si>
+    <t>Basic recipe creation and overview</t>
+  </si>
+  <si>
+    <t>When adding a meal specify a recipe</t>
+  </si>
+  <si>
+    <t>Add responsible logic to select user</t>
   </si>
 </sst>
 </file>
@@ -272,7 +306,50 @@
     <cellStyle name="Accent1" xfId="1" builtinId="29"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="28">
+  <dxfs count="42">
+    <dxf>
+      <numFmt numFmtId="1" formatCode="0"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
     <dxf>
       <numFmt numFmtId="1" formatCode="0"/>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
@@ -410,36 +487,73 @@
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{4572189F-29BF-400F-A010-14B1A3F85040}" name="Table15" displayName="Table15" ref="A1:F19" totalsRowShown="0" headerRowDxfId="13">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{4572189F-29BF-400F-A010-14B1A3F85040}" name="Table15" displayName="Table15" ref="A1:F19" totalsRowShown="0" headerRowDxfId="41">
   <tableColumns count="6">
-    <tableColumn id="1" xr3:uid="{F23DD78E-9832-4D69-9866-88B23B4C7197}" name="Task" dataDxfId="12"/>
-    <tableColumn id="2" xr3:uid="{12CE1293-031B-41E3-A384-99D9E64BE2AC}" name="Orig. Est." dataDxfId="11"/>
-    <tableColumn id="3" xr3:uid="{361FACD2-604B-42E1-951F-E479A19E4F68}" name="Cur. Est." dataDxfId="10"/>
-    <tableColumn id="4" xr3:uid="{04FF6573-A625-4DDA-A8A5-A0102C89B784}" name="Effort" dataDxfId="9"/>
-    <tableColumn id="5" xr3:uid="{4D2C2CFC-85E4-43DF-AE5D-FBB5274E2BB6}" name="Remain" dataDxfId="8"/>
-    <tableColumn id="6" xr3:uid="{65747612-EF52-4B83-9BB7-7096DDBA66E6}" name="Responsible" dataDxfId="7"/>
+    <tableColumn id="1" xr3:uid="{F23DD78E-9832-4D69-9866-88B23B4C7197}" name="Task" dataDxfId="40"/>
+    <tableColumn id="2" xr3:uid="{12CE1293-031B-41E3-A384-99D9E64BE2AC}" name="Orig. Est." dataDxfId="39"/>
+    <tableColumn id="3" xr3:uid="{361FACD2-604B-42E1-951F-E479A19E4F68}" name="Cur. Est." dataDxfId="38"/>
+    <tableColumn id="4" xr3:uid="{04FF6573-A625-4DDA-A8A5-A0102C89B784}" name="Effort" dataDxfId="37"/>
+    <tableColumn id="5" xr3:uid="{4D2C2CFC-85E4-43DF-AE5D-FBB5274E2BB6}" name="Remain" dataDxfId="36"/>
+    <tableColumn id="6" xr3:uid="{65747612-EF52-4B83-9BB7-7096DDBA66E6}" name="Responsible" dataDxfId="35"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{5198A3BB-CD99-4A50-BAE4-D470DD639E89}" name="Table26" displayName="Table26" ref="H1:J3" totalsRowShown="0" dataDxfId="6">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{5198A3BB-CD99-4A50-BAE4-D470DD639E89}" name="Table26" displayName="Table26" ref="H1:J3" totalsRowShown="0" dataDxfId="34">
   <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{F4ADF128-D9F1-4DF5-9ABE-6F3FCB334CE2}" name="Product Owner" dataDxfId="5"/>
-    <tableColumn id="2" xr3:uid="{EEED3716-B105-46BE-B2AA-AB2245881A37}" name="Scrum Master" dataDxfId="4"/>
-    <tableColumn id="3" xr3:uid="{E5E1E5D5-8404-49D4-ABF7-6AE9835F2022}" name="Team Members" dataDxfId="3"/>
+    <tableColumn id="1" xr3:uid="{F4ADF128-D9F1-4DF5-9ABE-6F3FCB334CE2}" name="Product Owner" dataDxfId="33"/>
+    <tableColumn id="2" xr3:uid="{EEED3716-B105-46BE-B2AA-AB2245881A37}" name="Scrum Master" dataDxfId="32"/>
+    <tableColumn id="3" xr3:uid="{E5E1E5D5-8404-49D4-ABF7-6AE9835F2022}" name="Team Members" dataDxfId="31"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight12" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{D3470464-FD92-4998-AE54-230A2D4B8316}" name="Table147" displayName="Table147" ref="A21:B25" totalsRowShown="0" headerRowDxfId="2">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{D3470464-FD92-4998-AE54-230A2D4B8316}" name="Table147" displayName="Table147" ref="A21:B25" totalsRowShown="0" headerRowDxfId="30">
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{1149A006-89B6-4B0D-9155-4EE279EE42E5}" name="User" dataDxfId="1"/>
-    <tableColumn id="2" xr3:uid="{4E4E6EE8-7212-48D4-B6CD-F579FD6C69B8}" name="Total" dataDxfId="0">
+    <tableColumn id="1" xr3:uid="{1149A006-89B6-4B0D-9155-4EE279EE42E5}" name="User" dataDxfId="29"/>
+    <tableColumn id="2" xr3:uid="{4E4E6EE8-7212-48D4-B6CD-F579FD6C69B8}" name="Total" dataDxfId="28">
       <calculatedColumnFormula>SUMIF($F$2:$F$18,Table147[[#This Row],[User]],$C$2:$C$18)</calculatedColumnFormula>
+    </tableColumn>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleLight9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table7.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{34242BC7-7BA1-47C2-B745-51E394732A0F}" name="Table158" displayName="Table158" ref="A1:F18" totalsRowShown="0" headerRowDxfId="13">
+  <tableColumns count="6">
+    <tableColumn id="1" xr3:uid="{A84DECB1-3973-4FB4-83EB-001BA7D765F0}" name="Task" dataDxfId="12"/>
+    <tableColumn id="2" xr3:uid="{DB9F8A42-1997-4E71-B3BB-439D10E4548A}" name="Orig. Est." dataDxfId="11"/>
+    <tableColumn id="3" xr3:uid="{E44059F1-DA21-4620-BFA7-49CA03E555C3}" name="Cur. Est." dataDxfId="10"/>
+    <tableColumn id="4" xr3:uid="{A6806941-EC6F-40CE-B8B0-3F6A5A45307C}" name="Effort" dataDxfId="9"/>
+    <tableColumn id="5" xr3:uid="{20854449-CB7E-4D4C-B02A-A9ACC270C59C}" name="Remain" dataDxfId="8"/>
+    <tableColumn id="6" xr3:uid="{DB8556E9-AE99-4718-89FC-8F25355ADEFC}" name="Responsible" dataDxfId="7"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleLight9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table8.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="8" xr:uid="{463E612C-BD1E-4CE9-A507-D55FB492CE9F}" name="Table269" displayName="Table269" ref="H1:J3" totalsRowShown="0" dataDxfId="6">
+  <tableColumns count="3">
+    <tableColumn id="1" xr3:uid="{3A999A87-AA72-4571-ADB8-AA4F179D1B5D}" name="Product Owner" dataDxfId="5"/>
+    <tableColumn id="2" xr3:uid="{D40B6100-AF84-4184-8BA8-1F162178A693}" name="Scrum Master" dataDxfId="4"/>
+    <tableColumn id="3" xr3:uid="{143EDB00-96BA-493C-9D7A-8110B287CC7C}" name="Team Members" dataDxfId="3"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleLight12" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table9.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="9" xr:uid="{C7E0C4CA-694A-4E5F-A220-097F881EDECB}" name="Table14710" displayName="Table14710" ref="A20:B24" totalsRowShown="0" headerRowDxfId="2">
+  <tableColumns count="2">
+    <tableColumn id="1" xr3:uid="{386B9E61-9DE1-4B79-AB63-23310EF88E38}" name="User" dataDxfId="1"/>
+    <tableColumn id="2" xr3:uid="{9A117063-BE1F-4990-9074-9282C3766F65}" name="Total" dataDxfId="0">
+      <calculatedColumnFormula>SUMIF($F$2:$F$17,Table14710[[#This Row],[User]],$C$2:$C$17)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
@@ -1225,11 +1339,11 @@
         <v>2</v>
       </c>
       <c r="D2" s="4">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E2" s="4">
         <f>Table15[[#This Row],[Cur. Est.]]-Table15[[#This Row],[Effort]]</f>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F2" s="9" t="s">
         <v>16</v>
@@ -1252,15 +1366,14 @@
         <v>2.5</v>
       </c>
       <c r="C3" s="4">
-        <f>Table15[[#This Row],[Orig. Est.]]</f>
-        <v>2.5</v>
+        <v>3</v>
       </c>
       <c r="D3" s="4">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E3" s="4">
         <f>Table15[[#This Row],[Cur. Est.]]-Table15[[#This Row],[Effort]]</f>
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="F3" s="9" t="s">
         <v>16</v>
@@ -1283,11 +1396,11 @@
         <v>3</v>
       </c>
       <c r="D4" s="4">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E4" s="4">
         <f>Table15[[#This Row],[Cur. Est.]]-Table15[[#This Row],[Effort]]</f>
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F4" s="9" t="s">
         <v>16</v>
@@ -1300,16 +1413,15 @@
       <c r="B5" s="4">
         <v>3</v>
       </c>
-      <c r="C5" s="4">
-        <f>Table15[[#This Row],[Orig. Est.]]</f>
-        <v>3</v>
-      </c>
-      <c r="D5" s="4">
-        <v>0</v>
+      <c r="C5" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="D5" s="8">
+        <v>0.5</v>
       </c>
       <c r="E5" s="4">
         <f>Table15[[#This Row],[Cur. Est.]]-Table15[[#This Row],[Effort]]</f>
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F5" s="9" t="s">
         <v>16</v>
@@ -1323,15 +1435,14 @@
         <v>4</v>
       </c>
       <c r="C6" s="4">
-        <f>Table15[[#This Row],[Orig. Est.]]</f>
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D6" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E6" s="4">
         <f>Table15[[#This Row],[Cur. Est.]]-Table15[[#This Row],[Effort]]</f>
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F6" s="9" t="s">
         <v>14</v>
@@ -1345,15 +1456,14 @@
         <v>4</v>
       </c>
       <c r="C7" s="4">
-        <f>Table15[[#This Row],[Orig. Est.]]</f>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D7" s="4">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E7" s="4">
         <f>Table15[[#This Row],[Cur. Est.]]-Table15[[#This Row],[Effort]]</f>
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F7" s="9" t="s">
         <v>14</v>
@@ -1371,11 +1481,11 @@
         <v>2</v>
       </c>
       <c r="D8" s="4">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E8" s="4">
         <f>Table15[[#This Row],[Cur. Est.]]-Table15[[#This Row],[Effort]]</f>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F8" s="9" t="s">
         <v>14</v>
@@ -1388,15 +1498,15 @@
       <c r="B9" s="4">
         <v>4</v>
       </c>
-      <c r="C9" s="4">
-        <v>6</v>
-      </c>
-      <c r="D9" s="4">
-        <v>0</v>
+      <c r="C9" s="8">
+        <v>4.5</v>
+      </c>
+      <c r="D9" s="8">
+        <v>4.5</v>
       </c>
       <c r="E9" s="4">
         <f>Table15[[#This Row],[Cur. Est.]]-Table15[[#This Row],[Effort]]</f>
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="F9" s="9" t="s">
         <v>15</v>
@@ -1410,15 +1520,14 @@
         <v>4</v>
       </c>
       <c r="C10" s="4">
-        <f>Table15[[#This Row],[Orig. Est.]]</f>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D10" s="4">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E10" s="4">
         <f>Table15[[#This Row],[Cur. Est.]]-Table15[[#This Row],[Effort]]</f>
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F10" s="9" t="s">
         <v>13</v>
@@ -1432,15 +1541,14 @@
         <v>3</v>
       </c>
       <c r="C11" s="4">
-        <f>Table15[[#This Row],[Orig. Est.]]</f>
         <v>3</v>
       </c>
       <c r="D11" s="4">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E11" s="4">
         <f>Table15[[#This Row],[Cur. Est.]]-Table15[[#This Row],[Effort]]</f>
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F11" s="9" t="s">
         <v>13</v>
@@ -1458,11 +1566,11 @@
         <v>1</v>
       </c>
       <c r="D12" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E12" s="4">
         <f>Table15[[#This Row],[Cur. Est.]]-Table15[[#This Row],[Effort]]</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F12" s="9" t="s">
         <v>13</v>
@@ -1480,11 +1588,11 @@
         <v>1</v>
       </c>
       <c r="D13" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E13" s="4">
         <f>Table15[[#This Row],[Cur. Est.]]-Table15[[#This Row],[Effort]]</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F13" s="9" t="s">
         <v>13</v>
@@ -1502,11 +1610,11 @@
         <v>3</v>
       </c>
       <c r="D14" s="4">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E14" s="4">
         <f>Table15[[#This Row],[Cur. Est.]]-Table15[[#This Row],[Effort]]</f>
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F14" s="9" t="s">
         <v>15</v>
@@ -1520,15 +1628,14 @@
         <v>3</v>
       </c>
       <c r="C15" s="4">
-        <f>Table15[[#This Row],[Orig. Est.]]</f>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D15" s="4">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E15" s="4">
         <f>Table15[[#This Row],[Cur. Est.]]-Table15[[#This Row],[Effort]]</f>
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F15" s="9" t="s">
         <v>13</v>
@@ -1542,15 +1649,14 @@
         <v>2</v>
       </c>
       <c r="C16" s="4">
-        <f>Table15[[#This Row],[Orig. Est.]]</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D16" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E16" s="4">
         <f>Table15[[#This Row],[Cur. Est.]]-Table15[[#This Row],[Effort]]</f>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F16" s="9" t="s">
         <v>15</v>
@@ -1568,11 +1674,11 @@
         <v>1</v>
       </c>
       <c r="D17" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E17" s="4">
         <f>Table15[[#This Row],[Cur. Est.]]-Table15[[#This Row],[Effort]]</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F17" s="9" t="s">
         <v>13</v>
@@ -1586,15 +1692,14 @@
         <v>2</v>
       </c>
       <c r="C18" s="4">
-        <f>Table15[[#This Row],[Orig. Est.]]</f>
         <v>2</v>
       </c>
       <c r="D18" s="4">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E18" s="4">
         <f>Table15[[#This Row],[Cur. Est.]]-Table15[[#This Row],[Effort]]</f>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F18" s="9" t="s">
         <v>14</v>
@@ -1610,15 +1715,15 @@
       </c>
       <c r="C19" s="7">
         <f t="shared" ref="C19:E19" si="0">SUM(C2:C18)</f>
-        <v>46.5</v>
+        <v>36</v>
       </c>
       <c r="D19" s="7">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="E19" s="7">
         <f t="shared" si="0"/>
-        <v>46.5</v>
+        <v>0</v>
       </c>
       <c r="F19" s="6" t="s">
         <v>20</v>
@@ -1638,7 +1743,7 @@
       </c>
       <c r="B22" s="4">
         <f>SUMIF($F$2:$F$18,Table147[[#This Row],[User]],$C$2:$C$18)</f>
-        <v>13</v>
+        <v>11</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.3">
@@ -1647,25 +1752,498 @@
       </c>
       <c r="B23" s="4">
         <f>SUMIF($F$2:$F$18,Table147[[#This Row],[User]],$C$2:$C$18)</f>
-        <v>12</v>
+        <v>8</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A24" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="B24" s="4">
+      <c r="B24" s="8">
         <f>SUMIF($F$2:$F$18,Table147[[#This Row],[User]],$C$2:$C$18)</f>
-        <v>11</v>
+        <v>8.5</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A25" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="B25" s="4">
+      <c r="B25" s="8">
         <f>SUMIF($F$2:$F$18,Table147[[#This Row],[User]],$C$2:$C$18)</f>
-        <v>10.5</v>
+        <v>8.5</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <tableParts count="3">
+    <tablePart r:id="rId1"/>
+    <tablePart r:id="rId2"/>
+    <tablePart r:id="rId3"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{33637D90-8CEA-4EC7-8FD9-A7AA2811F7E2}">
+  <dimension ref="A1:J24"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="32" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="8.44140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="7.88671875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="5.44140625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="7.33203125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.77734375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="13.88671875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="13.77734375" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.77734375" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="H1" t="s">
+        <v>10</v>
+      </c>
+      <c r="I1" t="s">
+        <v>11</v>
+      </c>
+      <c r="J1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>29</v>
+      </c>
+      <c r="B2" s="4">
+        <v>2</v>
+      </c>
+      <c r="C2" s="4">
+        <v>2</v>
+      </c>
+      <c r="D2" s="4">
+        <v>0</v>
+      </c>
+      <c r="E2" s="4">
+        <f>Table158[[#This Row],[Cur. Est.]]-Table158[[#This Row],[Effort]]</f>
+        <v>2</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="H2" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="I2" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="J2" s="3" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>30</v>
+      </c>
+      <c r="B3" s="4">
+        <v>4</v>
+      </c>
+      <c r="C3" s="4">
+        <v>4</v>
+      </c>
+      <c r="D3" s="4">
+        <v>0</v>
+      </c>
+      <c r="E3" s="4">
+        <f>Table158[[#This Row],[Cur. Est.]]-Table158[[#This Row],[Effort]]</f>
+        <v>4</v>
+      </c>
+      <c r="F3" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="H3" s="3"/>
+      <c r="I3" s="3"/>
+      <c r="J3" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>46</v>
+      </c>
+      <c r="B4" s="4">
+        <v>1</v>
+      </c>
+      <c r="C4" s="4">
+        <v>1</v>
+      </c>
+      <c r="D4" s="4">
+        <v>0</v>
+      </c>
+      <c r="E4" s="4">
+        <f>Table158[[#This Row],[Cur. Est.]]-Table158[[#This Row],[Effort]]</f>
+        <v>1</v>
+      </c>
+      <c r="F4" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>47</v>
+      </c>
+      <c r="B5" s="4">
+        <v>1</v>
+      </c>
+      <c r="C5" s="4">
+        <v>1</v>
+      </c>
+      <c r="D5" s="4">
+        <v>0</v>
+      </c>
+      <c r="E5" s="4">
+        <f>Table158[[#This Row],[Cur. Est.]]-Table158[[#This Row],[Effort]]</f>
+        <v>1</v>
+      </c>
+      <c r="F5" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>48</v>
+      </c>
+      <c r="B6" s="4">
+        <v>2</v>
+      </c>
+      <c r="C6" s="4">
+        <v>2</v>
+      </c>
+      <c r="D6" s="4">
+        <v>0</v>
+      </c>
+      <c r="E6" s="4">
+        <f>Table158[[#This Row],[Cur. Est.]]-Table158[[#This Row],[Effort]]</f>
+        <v>2</v>
+      </c>
+      <c r="F6" s="3" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>49</v>
+      </c>
+      <c r="B7" s="4">
+        <v>3</v>
+      </c>
+      <c r="C7" s="4">
+        <v>3</v>
+      </c>
+      <c r="D7" s="4">
+        <v>0</v>
+      </c>
+      <c r="E7" s="4">
+        <f>Table158[[#This Row],[Cur. Est.]]-Table158[[#This Row],[Effort]]</f>
+        <v>3</v>
+      </c>
+      <c r="F7" s="3" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>50</v>
+      </c>
+      <c r="B8" s="4">
+        <v>3</v>
+      </c>
+      <c r="C8" s="4">
+        <v>3</v>
+      </c>
+      <c r="D8" s="4">
+        <v>0</v>
+      </c>
+      <c r="E8" s="4">
+        <f>Table158[[#This Row],[Cur. Est.]]-Table158[[#This Row],[Effort]]</f>
+        <v>3</v>
+      </c>
+      <c r="F8" s="3" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>40</v>
+      </c>
+      <c r="B9" s="4">
+        <v>2</v>
+      </c>
+      <c r="C9" s="4">
+        <v>2</v>
+      </c>
+      <c r="D9" s="4">
+        <v>0</v>
+      </c>
+      <c r="E9" s="4">
+        <f>Table158[[#This Row],[Cur. Est.]]-Table158[[#This Row],[Effort]]</f>
+        <v>2</v>
+      </c>
+      <c r="F9" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
+        <v>39</v>
+      </c>
+      <c r="B10" s="4">
+        <v>3</v>
+      </c>
+      <c r="C10" s="4">
+        <v>3</v>
+      </c>
+      <c r="D10" s="4">
+        <v>0</v>
+      </c>
+      <c r="E10" s="4">
+        <f>Table158[[#This Row],[Cur. Est.]]-Table158[[#This Row],[Effort]]</f>
+        <v>3</v>
+      </c>
+      <c r="F10" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
+        <v>51</v>
+      </c>
+      <c r="B11" s="4">
+        <v>2</v>
+      </c>
+      <c r="C11" s="4">
+        <v>2</v>
+      </c>
+      <c r="D11" s="4">
+        <v>0</v>
+      </c>
+      <c r="E11" s="4">
+        <f>Table158[[#This Row],[Cur. Est.]]-Table158[[#This Row],[Effort]]</f>
+        <v>2</v>
+      </c>
+      <c r="F11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
+        <v>52</v>
+      </c>
+      <c r="B12" s="4">
+        <v>1</v>
+      </c>
+      <c r="C12" s="4">
+        <v>1</v>
+      </c>
+      <c r="D12" s="4">
+        <v>1</v>
+      </c>
+      <c r="E12" s="4">
+        <f>Table158[[#This Row],[Cur. Est.]]-Table158[[#This Row],[Effort]]</f>
+        <v>0</v>
+      </c>
+      <c r="F12" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A13" t="s">
+        <v>53</v>
+      </c>
+      <c r="B13" s="4">
+        <v>2</v>
+      </c>
+      <c r="C13" s="4">
+        <v>2</v>
+      </c>
+      <c r="D13" s="4">
+        <v>1</v>
+      </c>
+      <c r="E13" s="4">
+        <f>Table158[[#This Row],[Cur. Est.]]-Table158[[#This Row],[Effort]]</f>
+        <v>1</v>
+      </c>
+      <c r="F13" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A14" t="s">
+        <v>45</v>
+      </c>
+      <c r="B14" s="4">
+        <v>1</v>
+      </c>
+      <c r="C14" s="4">
+        <v>1</v>
+      </c>
+      <c r="D14" s="4">
+        <v>0</v>
+      </c>
+      <c r="E14" s="4">
+        <f>Table158[[#This Row],[Cur. Est.]]-Table158[[#This Row],[Effort]]</f>
+        <v>1</v>
+      </c>
+      <c r="F14" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A15" t="s">
+        <v>54</v>
+      </c>
+      <c r="B15" s="4">
+        <v>3</v>
+      </c>
+      <c r="C15" s="4">
+        <v>3</v>
+      </c>
+      <c r="D15" s="4">
+        <v>0</v>
+      </c>
+      <c r="E15" s="4">
+        <f>Table158[[#This Row],[Cur. Est.]]-Table158[[#This Row],[Effort]]</f>
+        <v>3</v>
+      </c>
+      <c r="F15" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A16" t="s">
+        <v>55</v>
+      </c>
+      <c r="B16" s="4">
+        <v>2</v>
+      </c>
+      <c r="C16" s="4">
+        <v>2</v>
+      </c>
+      <c r="D16" s="4">
+        <v>0</v>
+      </c>
+      <c r="E16" s="4">
+        <f>Table158[[#This Row],[Cur. Est.]]-Table158[[#This Row],[Effort]]</f>
+        <v>2</v>
+      </c>
+      <c r="F16" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A17" t="s">
+        <v>56</v>
+      </c>
+      <c r="B17" s="4">
+        <v>2</v>
+      </c>
+      <c r="C17" s="4">
+        <v>2</v>
+      </c>
+      <c r="D17" s="4">
+        <v>0</v>
+      </c>
+      <c r="E17" s="4">
+        <f>Table158[[#This Row],[Cur. Est.]]-Table158[[#This Row],[Effort]]</f>
+        <v>2</v>
+      </c>
+      <c r="F17" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A18" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="B18" s="7">
+        <f>SUM(B2:B17)</f>
+        <v>34</v>
+      </c>
+      <c r="C18" s="7">
+        <f>SUM(C2:C17)</f>
+        <v>34</v>
+      </c>
+      <c r="D18" s="7">
+        <f>SUM(D2:D17)</f>
+        <v>2</v>
+      </c>
+      <c r="E18" s="7">
+        <f>SUM(E2:E17)</f>
+        <v>32</v>
+      </c>
+      <c r="F18" s="6" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A20" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A21" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B21" s="4">
+        <f>SUMIF($F$2:$F$17,Table14710[[#This Row],[User]],$C$2:$C$17)</f>
+        <v>8</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A22" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B22" s="4">
+        <f>SUMIF($F$2:$F$17,Table14710[[#This Row],[User]],$C$2:$C$17)</f>
+        <v>10</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A23" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B23" s="4">
+        <f>SUMIF($F$2:$F$17,Table14710[[#This Row],[User]],$C$2:$C$17)</f>
+        <v>8</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A24" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B24" s="4">
+        <f>SUMIF($F$2:$F$17,Table14710[[#This Row],[User]],$C$2:$C$17)</f>
+        <v>8</v>
       </c>
     </row>
   </sheetData>

--- a/docs/effort-estimation.xlsx
+++ b/docs/effort-estimation.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vikto\Documents\HTL\3IHIF\WMC\room-food-docs\docs\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{766C7670-7861-4630-9AAD-211BA736D459}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DCC0E8C8-EA85-4708-A0BF-05C4A95E5ED8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{5CD19CBD-F40D-4B07-8DFB-09D007D4B786}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="2" xr2:uid="{5CD19CBD-F40D-4B07-8DFB-09D007D4B786}"/>
   </bookViews>
   <sheets>
     <sheet name="Sprint 1" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="155" uniqueCount="57">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="156" uniqueCount="58">
   <si>
     <t>Task</t>
   </si>
@@ -209,6 +209,9 @@
   </si>
   <si>
     <t>Add responsible logic to select user</t>
+  </si>
+  <si>
+    <t>x`</t>
   </si>
 </sst>
 </file>
@@ -487,35 +490,35 @@
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{4572189F-29BF-400F-A010-14B1A3F85040}" name="Table15" displayName="Table15" ref="A1:F19" totalsRowShown="0" headerRowDxfId="41">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{4572189F-29BF-400F-A010-14B1A3F85040}" name="Table15" displayName="Table15" ref="A1:F19" totalsRowShown="0" headerRowDxfId="13">
   <tableColumns count="6">
-    <tableColumn id="1" xr3:uid="{F23DD78E-9832-4D69-9866-88B23B4C7197}" name="Task" dataDxfId="40"/>
-    <tableColumn id="2" xr3:uid="{12CE1293-031B-41E3-A384-99D9E64BE2AC}" name="Orig. Est." dataDxfId="39"/>
-    <tableColumn id="3" xr3:uid="{361FACD2-604B-42E1-951F-E479A19E4F68}" name="Cur. Est." dataDxfId="38"/>
-    <tableColumn id="4" xr3:uid="{04FF6573-A625-4DDA-A8A5-A0102C89B784}" name="Effort" dataDxfId="37"/>
-    <tableColumn id="5" xr3:uid="{4D2C2CFC-85E4-43DF-AE5D-FBB5274E2BB6}" name="Remain" dataDxfId="36"/>
-    <tableColumn id="6" xr3:uid="{65747612-EF52-4B83-9BB7-7096DDBA66E6}" name="Responsible" dataDxfId="35"/>
+    <tableColumn id="1" xr3:uid="{F23DD78E-9832-4D69-9866-88B23B4C7197}" name="Task" dataDxfId="12"/>
+    <tableColumn id="2" xr3:uid="{12CE1293-031B-41E3-A384-99D9E64BE2AC}" name="Orig. Est." dataDxfId="11"/>
+    <tableColumn id="3" xr3:uid="{361FACD2-604B-42E1-951F-E479A19E4F68}" name="Cur. Est." dataDxfId="10"/>
+    <tableColumn id="4" xr3:uid="{04FF6573-A625-4DDA-A8A5-A0102C89B784}" name="Effort" dataDxfId="9"/>
+    <tableColumn id="5" xr3:uid="{4D2C2CFC-85E4-43DF-AE5D-FBB5274E2BB6}" name="Remain" dataDxfId="8"/>
+    <tableColumn id="6" xr3:uid="{65747612-EF52-4B83-9BB7-7096DDBA66E6}" name="Responsible" dataDxfId="7"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{5198A3BB-CD99-4A50-BAE4-D470DD639E89}" name="Table26" displayName="Table26" ref="H1:J3" totalsRowShown="0" dataDxfId="34">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{5198A3BB-CD99-4A50-BAE4-D470DD639E89}" name="Table26" displayName="Table26" ref="H1:J3" totalsRowShown="0" dataDxfId="6">
   <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{F4ADF128-D9F1-4DF5-9ABE-6F3FCB334CE2}" name="Product Owner" dataDxfId="33"/>
-    <tableColumn id="2" xr3:uid="{EEED3716-B105-46BE-B2AA-AB2245881A37}" name="Scrum Master" dataDxfId="32"/>
-    <tableColumn id="3" xr3:uid="{E5E1E5D5-8404-49D4-ABF7-6AE9835F2022}" name="Team Members" dataDxfId="31"/>
+    <tableColumn id="1" xr3:uid="{F4ADF128-D9F1-4DF5-9ABE-6F3FCB334CE2}" name="Product Owner" dataDxfId="5"/>
+    <tableColumn id="2" xr3:uid="{EEED3716-B105-46BE-B2AA-AB2245881A37}" name="Scrum Master" dataDxfId="4"/>
+    <tableColumn id="3" xr3:uid="{E5E1E5D5-8404-49D4-ABF7-6AE9835F2022}" name="Team Members" dataDxfId="3"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight12" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{D3470464-FD92-4998-AE54-230A2D4B8316}" name="Table147" displayName="Table147" ref="A21:B25" totalsRowShown="0" headerRowDxfId="30">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{D3470464-FD92-4998-AE54-230A2D4B8316}" name="Table147" displayName="Table147" ref="A21:B25" totalsRowShown="0" headerRowDxfId="2">
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{1149A006-89B6-4B0D-9155-4EE279EE42E5}" name="User" dataDxfId="29"/>
-    <tableColumn id="2" xr3:uid="{4E4E6EE8-7212-48D4-B6CD-F579FD6C69B8}" name="Total" dataDxfId="28">
+    <tableColumn id="1" xr3:uid="{1149A006-89B6-4B0D-9155-4EE279EE42E5}" name="User" dataDxfId="1"/>
+    <tableColumn id="2" xr3:uid="{4E4E6EE8-7212-48D4-B6CD-F579FD6C69B8}" name="Total" dataDxfId="0">
       <calculatedColumnFormula>SUMIF($F$2:$F$18,Table147[[#This Row],[User]],$C$2:$C$18)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -524,35 +527,35 @@
 </file>
 
 <file path=xl/tables/table7.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{34242BC7-7BA1-47C2-B745-51E394732A0F}" name="Table158" displayName="Table158" ref="A1:F18" totalsRowShown="0" headerRowDxfId="13">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{34242BC7-7BA1-47C2-B745-51E394732A0F}" name="Table158" displayName="Table158" ref="A1:F18" totalsRowShown="0" headerRowDxfId="41">
   <tableColumns count="6">
-    <tableColumn id="1" xr3:uid="{A84DECB1-3973-4FB4-83EB-001BA7D765F0}" name="Task" dataDxfId="12"/>
-    <tableColumn id="2" xr3:uid="{DB9F8A42-1997-4E71-B3BB-439D10E4548A}" name="Orig. Est." dataDxfId="11"/>
-    <tableColumn id="3" xr3:uid="{E44059F1-DA21-4620-BFA7-49CA03E555C3}" name="Cur. Est." dataDxfId="10"/>
-    <tableColumn id="4" xr3:uid="{A6806941-EC6F-40CE-B8B0-3F6A5A45307C}" name="Effort" dataDxfId="9"/>
-    <tableColumn id="5" xr3:uid="{20854449-CB7E-4D4C-B02A-A9ACC270C59C}" name="Remain" dataDxfId="8"/>
-    <tableColumn id="6" xr3:uid="{DB8556E9-AE99-4718-89FC-8F25355ADEFC}" name="Responsible" dataDxfId="7"/>
+    <tableColumn id="1" xr3:uid="{A84DECB1-3973-4FB4-83EB-001BA7D765F0}" name="Task" dataDxfId="40"/>
+    <tableColumn id="2" xr3:uid="{DB9F8A42-1997-4E71-B3BB-439D10E4548A}" name="Orig. Est." dataDxfId="39"/>
+    <tableColumn id="3" xr3:uid="{E44059F1-DA21-4620-BFA7-49CA03E555C3}" name="Cur. Est." dataDxfId="38"/>
+    <tableColumn id="4" xr3:uid="{A6806941-EC6F-40CE-B8B0-3F6A5A45307C}" name="Effort" dataDxfId="37"/>
+    <tableColumn id="5" xr3:uid="{20854449-CB7E-4D4C-B02A-A9ACC270C59C}" name="Remain" dataDxfId="36"/>
+    <tableColumn id="6" xr3:uid="{DB8556E9-AE99-4718-89FC-8F25355ADEFC}" name="Responsible" dataDxfId="35"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table8.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="8" xr:uid="{463E612C-BD1E-4CE9-A507-D55FB492CE9F}" name="Table269" displayName="Table269" ref="H1:J3" totalsRowShown="0" dataDxfId="6">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="8" xr:uid="{463E612C-BD1E-4CE9-A507-D55FB492CE9F}" name="Table269" displayName="Table269" ref="H1:J3" totalsRowShown="0" dataDxfId="34">
   <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{3A999A87-AA72-4571-ADB8-AA4F179D1B5D}" name="Product Owner" dataDxfId="5"/>
-    <tableColumn id="2" xr3:uid="{D40B6100-AF84-4184-8BA8-1F162178A693}" name="Scrum Master" dataDxfId="4"/>
-    <tableColumn id="3" xr3:uid="{143EDB00-96BA-493C-9D7A-8110B287CC7C}" name="Team Members" dataDxfId="3"/>
+    <tableColumn id="1" xr3:uid="{3A999A87-AA72-4571-ADB8-AA4F179D1B5D}" name="Product Owner" dataDxfId="33"/>
+    <tableColumn id="2" xr3:uid="{D40B6100-AF84-4184-8BA8-1F162178A693}" name="Scrum Master" dataDxfId="32"/>
+    <tableColumn id="3" xr3:uid="{143EDB00-96BA-493C-9D7A-8110B287CC7C}" name="Team Members" dataDxfId="31"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight12" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table9.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="9" xr:uid="{C7E0C4CA-694A-4E5F-A220-097F881EDECB}" name="Table14710" displayName="Table14710" ref="A20:B24" totalsRowShown="0" headerRowDxfId="2">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="9" xr:uid="{C7E0C4CA-694A-4E5F-A220-097F881EDECB}" name="Table14710" displayName="Table14710" ref="A20:B24" totalsRowShown="0" headerRowDxfId="30">
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{386B9E61-9DE1-4B79-AB63-23310EF88E38}" name="User" dataDxfId="1"/>
-    <tableColumn id="2" xr3:uid="{9A117063-BE1F-4990-9074-9282C3766F65}" name="Total" dataDxfId="0">
+    <tableColumn id="1" xr3:uid="{386B9E61-9DE1-4B79-AB63-23310EF88E38}" name="User" dataDxfId="29"/>
+    <tableColumn id="2" xr3:uid="{9A117063-BE1F-4990-9074-9282C3766F65}" name="Total" dataDxfId="28">
       <calculatedColumnFormula>SUMIF($F$2:$F$17,Table14710[[#This Row],[User]],$C$2:$C$17)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -1839,11 +1842,11 @@
         <v>2</v>
       </c>
       <c r="D2" s="4">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E2" s="4">
         <f>Table158[[#This Row],[Cur. Est.]]-Table158[[#This Row],[Effort]]</f>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F2" s="3" t="s">
         <v>16</v>
@@ -1863,17 +1866,17 @@
         <v>30</v>
       </c>
       <c r="B3" s="4">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C3" s="4">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D3" s="4">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="E3" s="4">
         <f>Table158[[#This Row],[Cur. Est.]]-Table158[[#This Row],[Effort]]</f>
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F3" s="3" t="s">
         <v>16</v>
@@ -1892,14 +1895,14 @@
         <v>1</v>
       </c>
       <c r="C4" s="4">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D4" s="4">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E4" s="4">
         <f>Table158[[#This Row],[Cur. Est.]]-Table158[[#This Row],[Effort]]</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F4" s="3" t="s">
         <v>16</v>
@@ -1913,14 +1916,14 @@
         <v>1</v>
       </c>
       <c r="C5" s="4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D5" s="4">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E5" s="4">
         <f>Table158[[#This Row],[Cur. Est.]]-Table158[[#This Row],[Effort]]</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F5" s="3" t="s">
         <v>16</v>
@@ -1934,14 +1937,14 @@
         <v>2</v>
       </c>
       <c r="C6" s="4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D6" s="4">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E6" s="4">
         <f>Table158[[#This Row],[Cur. Est.]]-Table158[[#This Row],[Effort]]</f>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F6" s="3" t="s">
         <v>15</v>
@@ -1952,17 +1955,17 @@
         <v>49</v>
       </c>
       <c r="B7" s="4">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C7" s="4">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D7" s="4">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="E7" s="4">
         <f>Table158[[#This Row],[Cur. Est.]]-Table158[[#This Row],[Effort]]</f>
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F7" s="3" t="s">
         <v>15</v>
@@ -1976,14 +1979,14 @@
         <v>3</v>
       </c>
       <c r="C8" s="4">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D8" s="4">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E8" s="4">
         <f>Table158[[#This Row],[Cur. Est.]]-Table158[[#This Row],[Effort]]</f>
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F8" s="3" t="s">
         <v>15</v>
@@ -2000,11 +2003,11 @@
         <v>2</v>
       </c>
       <c r="D9" s="4">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E9" s="4">
         <f>Table158[[#This Row],[Cur. Est.]]-Table158[[#This Row],[Effort]]</f>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F9" t="s">
         <v>13</v>
@@ -2018,14 +2021,14 @@
         <v>3</v>
       </c>
       <c r="C10" s="4">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D10" s="4">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E10" s="4">
         <f>Table158[[#This Row],[Cur. Est.]]-Table158[[#This Row],[Effort]]</f>
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F10" t="s">
         <v>13</v>
@@ -2042,11 +2045,11 @@
         <v>2</v>
       </c>
       <c r="D11" s="4">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E11" s="4">
         <f>Table158[[#This Row],[Cur. Est.]]-Table158[[#This Row],[Effort]]</f>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F11" t="s">
         <v>13</v>
@@ -2081,14 +2084,14 @@
         <v>2</v>
       </c>
       <c r="C13" s="4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D13" s="4">
         <v>1</v>
       </c>
       <c r="E13" s="4">
         <f>Table158[[#This Row],[Cur. Est.]]-Table158[[#This Row],[Effort]]</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F13" t="s">
         <v>14</v>
@@ -2105,11 +2108,11 @@
         <v>1</v>
       </c>
       <c r="D14" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E14" s="4">
         <f>Table158[[#This Row],[Cur. Est.]]-Table158[[#This Row],[Effort]]</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F14" t="s">
         <v>14</v>
@@ -2123,14 +2126,14 @@
         <v>3</v>
       </c>
       <c r="C15" s="4">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D15" s="4">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E15" s="4">
         <f>Table158[[#This Row],[Cur. Est.]]-Table158[[#This Row],[Effort]]</f>
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F15" t="s">
         <v>14</v>
@@ -2144,17 +2147,20 @@
         <v>2</v>
       </c>
       <c r="C16" s="4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D16" s="4">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E16" s="4">
         <f>Table158[[#This Row],[Cur. Est.]]-Table158[[#This Row],[Effort]]</f>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F16" t="s">
         <v>14</v>
+      </c>
+      <c r="J16" t="s">
+        <v>57</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.3">
@@ -2165,14 +2171,14 @@
         <v>2</v>
       </c>
       <c r="C17" s="4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D17" s="4">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E17" s="4">
         <f>Table158[[#This Row],[Cur. Est.]]-Table158[[#This Row],[Effort]]</f>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F17" t="s">
         <v>14</v>
@@ -2184,19 +2190,19 @@
       </c>
       <c r="B18" s="7">
         <f>SUM(B2:B17)</f>
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="C18" s="7">
         <f>SUM(C2:C17)</f>
-        <v>34</v>
+        <v>43</v>
       </c>
       <c r="D18" s="7">
         <f>SUM(D2:D17)</f>
-        <v>2</v>
+        <v>43</v>
       </c>
       <c r="E18" s="7">
         <f>SUM(E2:E17)</f>
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="F18" s="6" t="s">
         <v>20</v>
@@ -2216,7 +2222,7 @@
       </c>
       <c r="B21" s="4">
         <f>SUMIF($F$2:$F$17,Table14710[[#This Row],[User]],$C$2:$C$17)</f>
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.3">
@@ -2225,7 +2231,7 @@
       </c>
       <c r="B22" s="4">
         <f>SUMIF($F$2:$F$17,Table14710[[#This Row],[User]],$C$2:$C$17)</f>
-        <v>10</v>
+        <v>12</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.3">
@@ -2234,7 +2240,7 @@
       </c>
       <c r="B23" s="4">
         <f>SUMIF($F$2:$F$17,Table14710[[#This Row],[User]],$C$2:$C$17)</f>
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.3">
@@ -2243,7 +2249,7 @@
       </c>
       <c r="B24" s="4">
         <f>SUMIF($F$2:$F$17,Table14710[[#This Row],[User]],$C$2:$C$17)</f>
-        <v>8</v>
+        <v>12</v>
       </c>
     </row>
   </sheetData>
